--- a/files/Loan_Proposal.xlsx
+++ b/files/Loan_Proposal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bowjung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\team-file-center-main\team-file-center-main(เริ่มต้นก่อนทำlogin)\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7750FD03-DF58-47D2-9DEA-68AAF1D0513B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32076B5C-2CEC-4FBC-A9E6-4C4D4472D444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="ตารางคำนวณเบื้องต้น" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">เอกสารนำเสนอวงเงินกู้!$B$2:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">เอกสารนำเสนอวงเงินกู้!$B$2:$F$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
   <si>
     <t>1. ข้อมูลลูกค้า</t>
   </si>
@@ -235,8 +235,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="190" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="191" formatCode="0.000%"/>
+    <numFmt numFmtId="187" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="188" formatCode="0.000%"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -397,7 +397,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -443,12 +443,173 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7C9D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7C9D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7C9D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7C9D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7C9D6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -461,129 +622,210 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="6" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="191" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="191" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="0" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="0" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="8" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -608,15 +850,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>224460</xdr:colOff>
+      <xdr:colOff>280489</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>73302</xdr:rowOff>
+      <xdr:rowOff>62096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1619250</xdr:colOff>
+      <xdr:colOff>1675279</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>118778</xdr:rowOff>
+      <xdr:rowOff>107572</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -639,8 +881,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="529260" y="254277"/>
-          <a:ext cx="1394790" cy="397901"/>
+          <a:off x="583048" y="241390"/>
+          <a:ext cx="1394790" cy="392858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -940,484 +1182,475 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="3" max="3" width="9.625" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="14" customWidth="1"/>
-    <col min="5" max="5" width="13.625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="10" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="11"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="47"/>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C4" s="37"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="49"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E5" s="23"/>
+      <c r="F5" s="51"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E6" s="24"/>
+      <c r="F6" s="52"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="11"/>
+      <c r="D7" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E7" s="24"/>
+      <c r="F7" s="52"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="18" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E8" s="24"/>
+      <c r="F8" s="52"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="18" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C10" s="37"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="49"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="28" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E11" s="31"/>
+      <c r="F11" s="53"/>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="21">
+      <c r="C12" s="11"/>
+      <c r="D12" s="26">
         <v>800000</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="23" t="s">
+      <c r="E12" s="26"/>
+      <c r="F12" s="54" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="21">
+      <c r="C13" s="11"/>
+      <c r="D13" s="26">
         <v>800000</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="23" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="54" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20">
+      <c r="C14" s="11"/>
+      <c r="D14" s="22">
         <v>5</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="22"/>
+      <c r="F14" s="55" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="21">
+      <c r="C15" s="11"/>
+      <c r="D15" s="26">
         <v>12872</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="23" t="s">
+      <c r="E15" s="26"/>
+      <c r="F15" s="54" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20">
+      <c r="C16" s="11"/>
+      <c r="D16" s="22">
         <v>5</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="24" t="s">
+      <c r="E16" s="22"/>
+      <c r="F16" s="55" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="29">
+      <c r="C17" s="11"/>
+      <c r="D17" s="21">
         <f>SUM(D12+D15)</f>
         <v>812872</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="24" t="s">
+      <c r="E17" s="22"/>
+      <c r="F17" s="55" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="24"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C18" s="11"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="55"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <v>7.7899999999999997E-2</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="24"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E19" s="24"/>
+      <c r="F19" s="55"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <v>7.7899999999999997E-2</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="24"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E20" s="24"/>
+      <c r="F20" s="55"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <v>7.7899999999999997E-2</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="24"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E21" s="24"/>
+      <c r="F21" s="55"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="28">
         <v>8.0250000000000002E-2</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="25"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E22" s="28"/>
+      <c r="F22" s="57"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38">
+      <c r="C23" s="29"/>
+      <c r="D23" s="25">
         <v>7.7899999999999997E-2</v>
       </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="25"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E23" s="25"/>
+      <c r="F23" s="57"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="25"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C24" s="16"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="57"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="18">
         <v>18500</v>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="E25" s="18"/>
+      <c r="F25" s="61" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="31">
+      <c r="C26" s="17"/>
+      <c r="D26" s="18">
         <v>25000</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="E26" s="18"/>
+      <c r="F26" s="61" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C27" s="30"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="54"/>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="36"/>
-      <c r="D28" s="42">
+      <c r="C28" s="15"/>
+      <c r="D28" s="20">
         <v>9000</v>
       </c>
-      <c r="E28" s="42"/>
-      <c r="F28" s="33" t="s">
+      <c r="E28" s="20"/>
+      <c r="F28" s="65" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42">
+      <c r="C29" s="19"/>
+      <c r="D29" s="20">
         <v>19000</v>
       </c>
-      <c r="E29" s="42"/>
-      <c r="F29" s="33" t="s">
+      <c r="E29" s="20"/>
+      <c r="F29" s="65" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="49"/>
     </row>
     <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="68"/>
     </row>
     <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="70"/>
     </row>
     <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C33" s="37"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="49"/>
+    </row>
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="50" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="15"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E34" s="23"/>
+      <c r="F34" s="71"/>
+    </row>
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="71"/>
+    </row>
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1"/>
+      <c r="B36" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="18" t="s">
+      <c r="C36" s="2"/>
+      <c r="D36" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="15"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="8" t="s">
+      <c r="E36" s="24"/>
+      <c r="F36" s="71"/>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="73"/>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="76"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
+  <mergeCells count="38">
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B36:F37"/>
+    <mergeCell ref="B37:F38"/>
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B30:F30"/>
@@ -1431,9 +1664,31 @@
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
   </mergeCells>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1449,12 +1704,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
